--- a/plantillas/eleccion/Computo_Total_UT.xlsx
+++ b/plantillas/eleccion/Computo_Total_UT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\eleccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622D983-BD15-40EB-8582-F0890F30E30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF86F20D-54AF-4B88-8CE4-67D55EF18B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DC4B354-0937-4DDB-93B4-C1A86D17F2A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DC4B354-0937-4DDB-93B4-C1A86D17F2A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,12 +53,6 @@
     <t>Nombre(s)</t>
   </si>
   <si>
-    <t>Apellido Paterno</t>
-  </si>
-  <si>
-    <t>Apellido Materno</t>
-  </si>
-  <si>
     <t>Nombre de las Personas Candidatas</t>
   </si>
   <si>
@@ -78,6 +72,12 @@
   </si>
   <si>
     <t>Distrito</t>
+  </si>
+  <si>
+    <t>Primer Apellido</t>
+  </si>
+  <si>
+    <t>Segundo Apellido</t>
   </si>
 </sst>
 </file>
@@ -199,10 +199,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -570,7 +570,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="5"/>
@@ -610,20 +610,22 @@
       <c r="K6" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="J8" s="9" t="s">
-        <v>11</v>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="J9" s="9" t="s">
-        <v>12</v>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>0</v>
@@ -638,18 +640,18 @@
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -662,10 +664,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>

--- a/plantillas/eleccion/Computo_Total_UT.xlsx
+++ b/plantillas/eleccion/Computo_Total_UT.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF86F20D-54AF-4B88-8CE4-67D55EF18B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DC4B354-0937-4DDB-93B4-C1A86D17F2A5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DC4B354-0937-4DDB-93B4-C1A86D17F2A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
